--- a/l10n_it_lettera_intento/tests/data/account_invoice_line.xlsx
+++ b/l10n_it_lettera_intento/tests/data/account_invoice_line.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">l10n_generic_coa.conf_a_sale</t>
   </si>
   <si>
-    <t xml:space="preserve">z0bug.a8c2v</t>
+    <t xml:space="preserve">z0bug.tax_a8c2v</t>
   </si>
   <si>
     <t xml:space="preserve">z0bug.invoice_Z0_9_2</t>
